--- a/source/trip-template.xlsx
+++ b/source/trip-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oz.sharon/Development/JapanTripPwa-main/source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oz.sharon/Development/JapanTripPwa-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F32BF2C-8EFD-E844-9255-88C242868B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8CE80E-5360-174C-AD16-937FC1C7C613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20060" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="הגדרות" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2259" uniqueCount="1297">
   <si>
     <t>שדה</t>
   </si>
@@ -2836,9 +2836,6 @@
     <t>תעתיק</t>
   </si>
   <si>
-    <t>אוכל</t>
-  </si>
-  <si>
     <t>איננו אוכלים חזיר, ציר עצמות חזיר או שומן חזיר</t>
   </si>
   <si>
@@ -2885,6 +2882,1131 @@
   </si>
   <si>
     <t>Nimotsu o azukete mo ii desu ka?</t>
+  </si>
+  <si>
+    <t>אוכל וקניות</t>
+  </si>
+  <si>
+    <t>אני לא אוכל חזיר</t>
+  </si>
+  <si>
+    <t>私は豚肉食べません</t>
+  </si>
+  <si>
+    <t>Watashi wa butaniku tabemasen</t>
+  </si>
+  <si>
+    <t>כמה זה עולה?</t>
+  </si>
+  <si>
+    <t>これいくらですか？</t>
+  </si>
+  <si>
+    <t>Kore ikura desu ka?</t>
+  </si>
+  <si>
+    <t>על מה אתה ממליץ?</t>
+  </si>
+  <si>
+    <t>おすすめは何ですか？</t>
+  </si>
+  <si>
+    <t>Osusume wa nan desu ka?</t>
+  </si>
+  <si>
+    <t>את זה בבקשה</t>
+  </si>
+  <si>
+    <t>これをください</t>
+  </si>
+  <si>
+    <t>Kore onegai shimasu</t>
+  </si>
+  <si>
+    <t>אפשר לשלם באשראי?</t>
+  </si>
+  <si>
+    <t>カード使えますか？</t>
+  </si>
+  <si>
+    <t>Kaado tsukaemasu ka?</t>
+  </si>
+  <si>
+    <t>זה בסדר / לא צריך (מעולה לסירוב לשקית)</t>
+  </si>
+  <si>
+    <t>大丈夫です</t>
+  </si>
+  <si>
+    <t>Daijoubu desu</t>
+  </si>
+  <si>
+    <t>בלי [רכיב] בבקשה (מעולה להסרת ירקות/מרכיבים)</t>
+  </si>
+  <si>
+    <t>抜きでお願いします</t>
+  </si>
+  <si>
+    <t>... nuki de onegai shimasu</t>
+  </si>
+  <si>
+    <t>נימוסים ובסיס</t>
+  </si>
+  <si>
+    <t>סליחה / תסלח לי / מלצר</t>
+  </si>
+  <si>
+    <t>すみません</t>
+  </si>
+  <si>
+    <t>Sumimasen</t>
+  </si>
+  <si>
+    <t>תודה רבה</t>
+  </si>
+  <si>
+    <t>ありがとうございます</t>
+  </si>
+  <si>
+    <t>Arigatou gozaimasu</t>
+  </si>
+  <si>
+    <t>בבקשה / תתכבד</t>
+  </si>
+  <si>
+    <t>どうぞ</t>
+  </si>
+  <si>
+    <t>Douzo</t>
+  </si>
+  <si>
+    <t>מה שלומך?</t>
+  </si>
+  <si>
+    <t>元気ですか？</t>
+  </si>
+  <si>
+    <t>Genki desu ka?</t>
+  </si>
+  <si>
+    <t>אני לא מבין</t>
+  </si>
+  <si>
+    <t>分かりません</t>
+  </si>
+  <si>
+    <t>Wakarimasen</t>
+  </si>
+  <si>
+    <t>בבקשה (לבקשת שירות או פריט)</t>
+  </si>
+  <si>
+    <t>お願いします</t>
+  </si>
+  <si>
+    <t>Onegai shimasu</t>
+  </si>
+  <si>
+    <t>האם זו התחנה?</t>
+  </si>
+  <si>
+    <t>駅ですか？</t>
+  </si>
+  <si>
+    <t>Eki desu ka?</t>
+  </si>
+  <si>
+    <t>זה פה? / האם הגעתי למקום הנכון?</t>
+  </si>
+  <si>
+    <t>ここですか？</t>
+  </si>
+  <si>
+    <t>Koko desu ka?</t>
+  </si>
+  <si>
+    <t>תקשורת והסתדרות</t>
+  </si>
+  <si>
+    <t>האם אתה מדבר אנגלית?</t>
+  </si>
+  <si>
+    <t>英語話せますか？</t>
+  </si>
+  <si>
+    <t>Eigo ga hanasemasu ka?</t>
+  </si>
+  <si>
+    <t>עוד פעם אחת בבקשה</t>
+  </si>
+  <si>
+    <t>もう一度お願いします</t>
+  </si>
+  <si>
+    <t>Mou ichido onegai shimasu</t>
+  </si>
+  <si>
+    <t>איפה השירותים?</t>
+  </si>
+  <si>
+    <t>トイレはどこですか？</t>
+  </si>
+  <si>
+    <t>Toire wa doko desu ka?</t>
+  </si>
+  <si>
+    <t>מפה</t>
+  </si>
+  <si>
+    <t>地図</t>
+  </si>
+  <si>
+    <t>Chizu</t>
+  </si>
+  <si>
+    <t>yakiniku-rokkasen</t>
+  </si>
+  <si>
+    <t>שינג'וקו</t>
+  </si>
+  <si>
+    <t>Yakiniku Rokkasen</t>
+  </si>
+  <si>
+    <t>יאקיניקו / בקר</t>
+  </si>
+  <si>
+    <t>¥8,000–15,000</t>
+  </si>
+  <si>
+    <t>בקר / ברביקיו עצמי (לשאול על רוטב)</t>
+  </si>
+  <si>
+    <t>תפריט הכל כולל בקר וואגיו</t>
+  </si>
+  <si>
+    <t>Yakiniku Rokkasen Shinjuku Tokyo</t>
+  </si>
+  <si>
+    <t>https://rokkasen.co.jp/</t>
+  </si>
+  <si>
+    <t>חוויית ברביקיו עצמי (יאקיניקו) עם תפריטי הכל כלול, מומלץ להזמין מקום מראש</t>
+  </si>
+  <si>
+    <t>han-no-daidokoro</t>
+  </si>
+  <si>
+    <t>Han no Daidokoro / Bettei</t>
+  </si>
+  <si>
+    <t>יאקיניקו / וואגיו קוריאני</t>
+  </si>
+  <si>
+    <t>¥5,000–10,000</t>
+  </si>
+  <si>
+    <t>בקר וואגיו (לבדוק רכיבי רטבים)</t>
+  </si>
+  <si>
+    <t>נתחי וואגיו מובחרים</t>
+  </si>
+  <si>
+    <t>Han no Daidokoro Bettei Shibuya Tokyo</t>
+  </si>
+  <si>
+    <t>ואגיו קוריאני מעולה ויאקיניקו עם שירות מצוין</t>
+  </si>
+  <si>
+    <t>jambo-hanare</t>
+  </si>
+  <si>
+    <t>הונגו / טוקיו</t>
+  </si>
+  <si>
+    <t>Yakiniku Jambo Hanare</t>
+  </si>
+  <si>
+    <t>יאקיניקו וואגיו</t>
+  </si>
+  <si>
+    <t>¥10,000–20,000</t>
+  </si>
+  <si>
+    <t>בקר בלבד</t>
+  </si>
+  <si>
+    <t>ארוחת וואגיו משובחת (Nohara Yaki)</t>
+  </si>
+  <si>
+    <t>Yakiniku Jambo Hanare Tokyo</t>
+  </si>
+  <si>
+    <t>ארוחת וואגיו משובחת ברמה גבוהה מאוד</t>
+  </si>
+  <si>
+    <t>ginza-steak-honten</t>
+  </si>
+  <si>
+    <t>Ginza Steak Honten</t>
+  </si>
+  <si>
+    <t>סטייק וואגיו</t>
+  </si>
+  <si>
+    <t>¥7,000–12,000</t>
+  </si>
+  <si>
+    <t>בקר וואגיו</t>
+  </si>
+  <si>
+    <t>תפריט אכול כפי יכולתך וואגיו</t>
+  </si>
+  <si>
+    <t>Ginza Steak Honten Tokyo</t>
+  </si>
+  <si>
+    <t>חוויית וואגיו בסגנון אכול כפי יכולתך</t>
+  </si>
+  <si>
+    <t>coco-nemaru-ginza</t>
+  </si>
+  <si>
+    <t>Coco Nemaru Ginza</t>
+  </si>
+  <si>
+    <t>¥6,000–12,000</t>
+  </si>
+  <si>
+    <t>סטייק וואגיו איכותי</t>
+  </si>
+  <si>
+    <t>Coco Nemaru Ginza Tokyo</t>
+  </si>
+  <si>
+    <t>סטייק וואגיו איכותי במרכז גינזה</t>
+  </si>
+  <si>
+    <t>wagyu-burger-hirokiya</t>
+  </si>
+  <si>
+    <t>שיבויה / איביסו</t>
+  </si>
+  <si>
+    <t>WAGYU BURGER HIROKIYA</t>
+  </si>
+  <si>
+    <t>המבורגר וואגיו</t>
+  </si>
+  <si>
+    <t>¥2,000–4,000</t>
+  </si>
+  <si>
+    <t>המבורגר בקר וואגיו</t>
+  </si>
+  <si>
+    <t>המבורגר וואגיו קלאסי או צ'דר</t>
+  </si>
+  <si>
+    <t>WAGYU BURGER HIROKIYA Tokyo</t>
+  </si>
+  <si>
+    <t>המבורגרים מנתחי וואגיו איכותיים</t>
+  </si>
+  <si>
+    <t>yoroniku</t>
+  </si>
+  <si>
+    <t>אאויאמה / מינאטו</t>
+  </si>
+  <si>
+    <t>Yoroniku</t>
+  </si>
+  <si>
+    <t>יאקיניקו אומקסה</t>
+  </si>
+  <si>
+    <t>¥12,000–20,000</t>
+  </si>
+  <si>
+    <t>בקר וואגיו בלבד</t>
+  </si>
+  <si>
+    <t>תפריט אומקסה וואגיו</t>
+  </si>
+  <si>
+    <t>Yoroniku Aoyama Tokyo</t>
+  </si>
+  <si>
+    <t>ארוחת אומקסה (תפריט שף) המוקדשת כולה לוואגיו</t>
+  </si>
+  <si>
+    <t>rare-tendon-mitsuyoshi</t>
+  </si>
+  <si>
+    <t>Rare Tendon Ginza Mitsuyoshi</t>
+  </si>
+  <si>
+    <t>טנדון / וואגיו ודגים</t>
+  </si>
+  <si>
+    <t>¥2,500–5,000</t>
+  </si>
+  <si>
+    <t>קערות אורז עם וואגיו או דגים</t>
+  </si>
+  <si>
+    <t>טמפורה וואגיו נדירה</t>
+  </si>
+  <si>
+    <t>Rare Tendon Ginza Mitsuyoshi Tokyo</t>
+  </si>
+  <si>
+    <t>קערות אורז עם טמפורה של וואגיו או דגים בגינזה</t>
+  </si>
+  <si>
+    <t>gyukatsu-motomura</t>
+  </si>
+  <si>
+    <t>שינג'וקו / שיבויה</t>
+  </si>
+  <si>
+    <t>Gyukatsu Motomura</t>
+  </si>
+  <si>
+    <t>גיוקאטסו (שניצל בקר)</t>
+  </si>
+  <si>
+    <t>¥1,500–2,500</t>
+  </si>
+  <si>
+    <t>בקר בלבד (ללא חזיר)</t>
+  </si>
+  <si>
+    <t>סט שניצל בקר וואגיו לטיגון עצמי</t>
+  </si>
+  <si>
+    <t>Gyukatsu Motomura Shinjuku Tokyo</t>
+  </si>
+  <si>
+    <t>רשת פופולרית מאוד שמגישה שניצל בקר (גיוקאטסו) המטוגן קלות על אבן חמה</t>
+  </si>
+  <si>
+    <t>asakusa-menchi</t>
+  </si>
+  <si>
+    <t>Asakusa Menchi</t>
+  </si>
+  <si>
+    <t>אוכל רחוב / קרוקט</t>
+  </si>
+  <si>
+    <t>¥300–500</t>
+  </si>
+  <si>
+    <t>⚠️ מכיל חזיר! (תערובת בקר קובי וחזיר)</t>
+  </si>
+  <si>
+    <t>קרוקט מנצ'י</t>
+  </si>
+  <si>
+    <t>Asakusa Menchi Tokyo</t>
+  </si>
+  <si>
+    <t>⚠️ מכיל חזיר! (לא מומלץ לשומרי חזיר). הקרוקט מכיל תערובת בקר וחזיר</t>
+  </si>
+  <si>
+    <t>konbini-egg-onigiri</t>
+  </si>
+  <si>
+    <t>כללי (קונביני)</t>
+  </si>
+  <si>
+    <t>FamilyMart / 7-Eleven (כריך ביצים / אוניגירי)</t>
+  </si>
+  <si>
+    <t>אוכל מהיר / קונביני</t>
+  </si>
+  <si>
+    <t>¥150–400</t>
+  </si>
+  <si>
+    <t>ללא חזיר (כריכי ביצים, אוניגירי סלמון/טונה מיונז)</t>
+  </si>
+  <si>
+    <t>כריך ביצים, אוניגירי סלמון</t>
+  </si>
+  <si>
+    <t>7-Eleven Tokyo</t>
+  </si>
+  <si>
+    <t>כריכי הביצים המפורסמים והאוניגירי הבסיסיים אינם מכילים חזיר</t>
+  </si>
+  <si>
+    <t>ichiran-no-pork</t>
+  </si>
+  <si>
+    <t>שינג'וקו / אסאקוסה</t>
+  </si>
+  <si>
+    <t>Ichiran No Pork (Nishi-Shinjuku / Asakusa)</t>
+  </si>
+  <si>
+    <t>ראמן עוף/בקר</t>
+  </si>
+  <si>
+    <t>¥1,200–2,000</t>
+  </si>
+  <si>
+    <t>100% ללא חזיר (ציר עוף ובקר)</t>
+  </si>
+  <si>
+    <t>100% Tonkotsu-Free Ramen</t>
+  </si>
+  <si>
+    <t>Ichiran No Pork Nishi-Shinjuku Tokyo</t>
+  </si>
+  <si>
+    <t>הגרסה הנקייה מחזיר של הרשת האייקונית, המבוססת על ציר עוף ובקר</t>
+  </si>
+  <si>
+    <t>ayam-ya-tokyo</t>
+  </si>
+  <si>
+    <t>אואנו / אסאקוסה</t>
+  </si>
+  <si>
+    <t>Ayam-Ya Okachimachi</t>
+  </si>
+  <si>
+    <t>ראמן חלאל</t>
+  </si>
+  <si>
+    <t>¥1,000–1,500</t>
+  </si>
+  <si>
+    <t>חלאל מוסמך, ללא חזיר</t>
+  </si>
+  <si>
+    <t>Tori Paitan Ramen</t>
+  </si>
+  <si>
+    <t>Ayam Ya Okachimachi Tokyo</t>
+  </si>
+  <si>
+    <t>ראמן על בסיס ציר עוף סמיך ועשיר (Tori Paitan) עם תעודת חלאל</t>
+  </si>
+  <si>
+    <t>kikanbo-miso-ramen</t>
+  </si>
+  <si>
+    <t>איקבוקורו / קאנדה</t>
+  </si>
+  <si>
+    <t>Karashibi Kikanbo Miso Ramen</t>
+  </si>
+  <si>
+    <t>ראמן מיסו חריף</t>
+  </si>
+  <si>
+    <t>⚠️ מכיל חזיר! (Chashu וציר חזיר)</t>
+  </si>
+  <si>
+    <t>Kara Miso Ramen</t>
+  </si>
+  <si>
+    <t>Karashibi Kikanbo Ikebukuro Tokyo</t>
+  </si>
+  <si>
+    <t>⚠️ מכיל חזיר! (לא מומלץ לשומרי חזיר). מוגש עם נתח חזיר וציר מבוסס חזיר</t>
+  </si>
+  <si>
+    <t>shodai-ebisu</t>
+  </si>
+  <si>
+    <t>איביסו / שיבויה</t>
+  </si>
+  <si>
+    <t>Shodai</t>
+  </si>
+  <si>
+    <t>קארי אודון</t>
+  </si>
+  <si>
+    <t>לשאול על ציר המרק (אודון קארי)</t>
+  </si>
+  <si>
+    <t>Curry Udon עם קציפת תפוחי אדמה</t>
+  </si>
+  <si>
+    <t>Shodai Ebisu Tokyo</t>
+  </si>
+  <si>
+    <t>קארי אודון ייחודי המוגש עם קציפת תפוחי אדמה מוקצפת מעל</t>
+  </si>
+  <si>
+    <t>afuri-ramen</t>
+  </si>
+  <si>
+    <t>הרבוקו / שיבויה / איביסו</t>
+  </si>
+  <si>
+    <t>Afuri Ramen</t>
+  </si>
+  <si>
+    <t>ראמן יוג'ו/עוף</t>
+  </si>
+  <si>
+    <t>¥1,100–1,800</t>
+  </si>
+  <si>
+    <t>אופציית ציר עוף עדין / אופציה טבעונית</t>
+  </si>
+  <si>
+    <t>Yuzu Shio Ramen / Vegan Ramen</t>
+  </si>
+  <si>
+    <t>Afuri Harajuku Tokyo</t>
+  </si>
+  <si>
+    <t>https://afuri.com/</t>
+  </si>
+  <si>
+    <t>רשת ראמן פופולרית (כוללת ציר עוף עדין עם יוזו, וגם אופציה טבעונית מלאה)</t>
+  </si>
+  <si>
+    <t>tokyo-abura-gumi</t>
+  </si>
+  <si>
+    <t>Tokyo Abura Gumi Main Store</t>
+  </si>
+  <si>
+    <t>אבורה סוֹבָּה (ראמן יבש)</t>
+  </si>
+  <si>
+    <t>¥900–1,400</t>
+  </si>
+  <si>
+    <t>לבדוק תוספות (חלק מהרטבים מכילים שומן חזיר)</t>
+  </si>
+  <si>
+    <t>Abura Soba</t>
+  </si>
+  <si>
+    <t>Tokyo Abura Gumi Shinjuku Tokyo</t>
+  </si>
+  <si>
+    <t>ראמן ייחודי ללא מרק (נאכל עם חומץ ושמן צ'ילי)</t>
+  </si>
+  <si>
+    <t>men-mtsui</t>
+  </si>
+  <si>
+    <t>men mtsui</t>
+  </si>
+  <si>
+    <t>ראמן סויה</t>
+  </si>
+  <si>
+    <t>ראמן סויה (לבדוק רכיבי ציר)</t>
+  </si>
+  <si>
+    <t>Shoyu Ramen</t>
+  </si>
+  <si>
+    <t>men mtsui Asakusa Tokyo</t>
+  </si>
+  <si>
+    <t>מנת ראמן איכותית על בסיס סויה</t>
+  </si>
+  <si>
+    <t>kaiten-sushi-ginza-onodera</t>
+  </si>
+  <si>
+    <t>גינזה / אומטסנדו</t>
+  </si>
+  <si>
+    <t>Kaiten Sushi Ginza Onodera</t>
+  </si>
+  <si>
+    <t>סושי מסוע פרימיום</t>
+  </si>
+  <si>
+    <t>¥3,000–7,000</t>
+  </si>
+  <si>
+    <t>מבוסס דגים מוסמך</t>
+  </si>
+  <si>
+    <t>טונה טרייה, סלמון, אוני</t>
+  </si>
+  <si>
+    <t>Kaiten Sushi Ginza Onodera Tokyo</t>
+  </si>
+  <si>
+    <t>חוויית סושי מסוע איכותית ברמת פרימיום בגינזה</t>
+  </si>
+  <si>
+    <t>kaiten-sushi-toriton</t>
+  </si>
+  <si>
+    <t>איקבוקורו / סקייטרי</t>
+  </si>
+  <si>
+    <t>KAITEN SUSHI TORITON</t>
+  </si>
+  <si>
+    <t>סושי מסוע</t>
+  </si>
+  <si>
+    <t>דגים ופירות ים</t>
+  </si>
+  <si>
+    <t>דגי הוקאידו טריים</t>
+  </si>
+  <si>
+    <t>Kaiten Sushi Toriton Ikebukuro Tokyo</t>
+  </si>
+  <si>
+    <t>סושי מסוע פופולרי ומעולה שמקורו בהוקאידו</t>
+  </si>
+  <si>
+    <t>seagen-tsukiji</t>
+  </si>
+  <si>
+    <t>צוקיג'י</t>
+  </si>
+  <si>
+    <t>Seagen Restaurants in Tsukiji</t>
+  </si>
+  <si>
+    <t>סושי / קערות אורז ודגים</t>
+  </si>
+  <si>
+    <t>¥2,000–5,000</t>
+  </si>
+  <si>
+    <t>100% דגים ופירות ים</t>
+  </si>
+  <si>
+    <t>Kaisen-don (קערת אורז ודגים)</t>
+  </si>
+  <si>
+    <t>Seagen Tsukiji Tokyo</t>
+  </si>
+  <si>
+    <t>מסעדת דגים וסושי בשוק צוקיג'י</t>
+  </si>
+  <si>
+    <t>hakkoku-sushi</t>
+  </si>
+  <si>
+    <t>Hakkoku</t>
+  </si>
+  <si>
+    <t>סושי אומקסה</t>
+  </si>
+  <si>
+    <t>¥15,000–30,000</t>
+  </si>
+  <si>
+    <t>ארוחת אומקסה שף</t>
+  </si>
+  <si>
+    <t>Hakkoku Ginza Tokyo</t>
+  </si>
+  <si>
+    <t>סושי אומקסה (ארוחת שף) ברמה גבוהה מאוד</t>
+  </si>
+  <si>
+    <t>sushi-kenshin</t>
+  </si>
+  <si>
+    <t>Sushi Kenshin</t>
+  </si>
+  <si>
+    <t>סושי אומקסה מסורתי</t>
+  </si>
+  <si>
+    <t>¥12,000–25,000</t>
+  </si>
+  <si>
+    <t>תפריט אומקסה מסורתי</t>
+  </si>
+  <si>
+    <t>Sushi Kenshin Ginza Tokyo</t>
+  </si>
+  <si>
+    <t>חוויית סושי אומקסה מסורתית ויוקרתית</t>
+  </si>
+  <si>
+    <t>uogashi-nihon-ichi</t>
+  </si>
+  <si>
+    <t>שיבויה Dogenzaka</t>
+  </si>
+  <si>
+    <t>Uogashi Nihon-Ichi (Shibuya Dogenzaka)</t>
+  </si>
+  <si>
+    <t>סושי בעמידה</t>
+  </si>
+  <si>
+    <t>¥1,500–3,000</t>
+  </si>
+  <si>
+    <t>דגים טריים בלבד</t>
+  </si>
+  <si>
+    <t>ניגירי סלמון, טונה וניגירי צרוב</t>
+  </si>
+  <si>
+    <t>Uogashi Nihon-Ichi Shibuya Dogenzaka Tokyo</t>
+  </si>
+  <si>
+    <t>חוויה מקומית מהירה וטעימה של סושי בעמידה</t>
+  </si>
+  <si>
+    <t>maguro-mart</t>
+  </si>
+  <si>
+    <t>נאקאנו / טוקיו</t>
+  </si>
+  <si>
+    <t>Maguro Mart</t>
+  </si>
+  <si>
+    <t>מסעדת טונה</t>
+  </si>
+  <si>
+    <t>¥3,000–6,000</t>
+  </si>
+  <si>
+    <t>דגי טונה ופירות ים בלבד</t>
+  </si>
+  <si>
+    <t>מגש נתחי טונה מגוונים לצלייה/נא</t>
+  </si>
+  <si>
+    <t>Maguro Mart Nakano Tokyo</t>
+  </si>
+  <si>
+    <t>מסעדה ייחודית המוקדשת כולה לארוחות טונה יצירתיות</t>
+  </si>
+  <si>
+    <t>udatsu-sushi</t>
+  </si>
+  <si>
+    <t>נאקאמגורו</t>
+  </si>
+  <si>
+    <t>Udatsu Sushi</t>
+  </si>
+  <si>
+    <t>¥25,000–40,000</t>
+  </si>
+  <si>
+    <t>דגים</t>
+  </si>
+  <si>
+    <t>אומקסה</t>
+  </si>
+  <si>
+    <t>Udatsu Sushi Nakameguro Tokyo</t>
+  </si>
+  <si>
+    <t>⚠️ לא מומלץ! (הערת המדריך: יקר מדי ולא מומלץ ללכת)</t>
+  </si>
+  <si>
+    <t>kura-sushiro</t>
+  </si>
+  <si>
+    <t>שינג'וקו / שיבויה / כללי</t>
+  </si>
+  <si>
+    <t>Kura Sushi / Sushiro</t>
+  </si>
+  <si>
+    <t>סושי מסוע טכנולוגי</t>
+  </si>
+  <si>
+    <t>¥1,000–2,500</t>
+  </si>
+  <si>
+    <t>מבוסס דגים (להיזהר ממרקים/תוספות עוף או חזיר)</t>
+  </si>
+  <si>
+    <t>מגוון ניגירי דגים</t>
+  </si>
+  <si>
+    <t>Kura Sushi Shinjuku Tokyo</t>
+  </si>
+  <si>
+    <t>רשתות סושי מסוע טכנולוגיות וזולות מבוססות דגים</t>
+  </si>
+  <si>
+    <t>tsukiji-strawberry-daifuku</t>
+  </si>
+  <si>
+    <t>Tsukiji Strawberry Daifuku Market Stalls</t>
+  </si>
+  <si>
+    <t>קינוחים / מתוקים</t>
+  </si>
+  <si>
+    <t>¥400–800</t>
+  </si>
+  <si>
+    <t>צמחוני / מתוק</t>
+  </si>
+  <si>
+    <t>מוצ'י דאיפוקו תות טרי</t>
+  </si>
+  <si>
+    <t>דוכן בשוק הדגים Tsukiji: מוצ'י דאיפוקו טרי (קינוח אורז מתוק עם תותים)</t>
+  </si>
+  <si>
+    <t>musashi-no-mori-coffee</t>
+  </si>
+  <si>
+    <t>שינג'וקו / טוקיו</t>
+  </si>
+  <si>
+    <t>Musashi no Mori Coffee</t>
+  </si>
+  <si>
+    <t>בית קפה / פנקייק</t>
+  </si>
+  <si>
+    <t>¥1,000–2,000</t>
+  </si>
+  <si>
+    <t>חלבי / צמחוני</t>
+  </si>
+  <si>
+    <t>פנקייק פלאפי אוורירי</t>
+  </si>
+  <si>
+    <t>Musashi no Mori Coffee Tokyo</t>
+  </si>
+  <si>
+    <t>בית קפה המגיש פנקייק פלאפי ואוורירי מדהים</t>
+  </si>
+  <si>
+    <t>sugamo-street-food</t>
+  </si>
+  <si>
+    <t>סוגאמו (שינטוקיו)</t>
+  </si>
+  <si>
+    <t>Sugamo Shopping Street</t>
+  </si>
+  <si>
+    <t>אוכל רחוב אתגרי</t>
+  </si>
+  <si>
+    <t>¥300–800</t>
+  </si>
+  <si>
+    <t>חגבים (חרקים)</t>
+  </si>
+  <si>
+    <t>חגבים מתובלים</t>
+  </si>
+  <si>
+    <t>Sugamo Jizodori Shopping Street Tokyo</t>
+  </si>
+  <si>
+    <t>שוק Sugamo: חגבים (לחובבי האתגרים)</t>
+  </si>
+  <si>
+    <t>age-3-fried-sandwich</t>
+  </si>
+  <si>
+    <t>Age 3 Ginza</t>
+  </si>
+  <si>
+    <t>כריך מטוגן</t>
+  </si>
+  <si>
+    <t>¥500–1,000</t>
+  </si>
+  <si>
+    <t>מגוון מילויים</t>
+  </si>
+  <si>
+    <t>Age 3 Ginza Tokyo</t>
+  </si>
+  <si>
+    <t>⚠️ לא מומלץ! (הערת המדריך: לא מומלץ בכלל)</t>
+  </si>
+  <si>
+    <t>pizza-pst</t>
+  </si>
+  <si>
+    <t>רופונגי / היגאשי-אזאבו</t>
+  </si>
+  <si>
+    <t>Pizza PST (Pizza Studio Tamaki)</t>
+  </si>
+  <si>
+    <t>פיצה איטלקית</t>
+  </si>
+  <si>
+    <t>לבחור פיצה מרגריטה / ללא נקניק חזיר</t>
+  </si>
+  <si>
+    <t>Pizza Tamaki / Margherita</t>
+  </si>
+  <si>
+    <t>Pizza Studio Tamaki Higashi Azabu Tokyo</t>
+  </si>
+  <si>
+    <t>פיצה מעולה וזוכת פרסים בטוקיו</t>
+  </si>
+  <si>
+    <t>aramaki-yakitori</t>
+  </si>
+  <si>
+    <t>גינזה / אסאקוסה</t>
+  </si>
+  <si>
+    <t>Aramaki Yakitori</t>
+  </si>
+  <si>
+    <t>יקיטורי (שיפודי עוף)</t>
+  </si>
+  <si>
+    <t>¥4,000–8,000</t>
+  </si>
+  <si>
+    <t>שיפודי עוף (ללא חזיר)</t>
+  </si>
+  <si>
+    <t>סט שיפודי עוף מובחרים</t>
+  </si>
+  <si>
+    <t>Aramaki Yakitori Tokyo</t>
+  </si>
+  <si>
+    <t>שיפודי יקיטורי (עוף) מומלצי מדריך מישלן</t>
+  </si>
+  <si>
+    <t>misono-kyoto</t>
+  </si>
+  <si>
+    <t>קיוטו (מרכז העיר)</t>
+  </si>
+  <si>
+    <t>Misono Kyoto</t>
+  </si>
+  <si>
+    <t>טפניאקי / סטייק וואגיו</t>
+  </si>
+  <si>
+    <t>¥10,000–25,000</t>
+  </si>
+  <si>
+    <t>ארוחת סטייק טפניאקי שף</t>
+  </si>
+  <si>
+    <t>Misono Teppanyaki Kyoto</t>
+  </si>
+  <si>
+    <t>חוויית טפניאקי יוקרתית — שף פרטי שמכין סטייקים על פלטת ברזל עם שואו מרהיב</t>
+  </si>
+  <si>
+    <t>ayam-ya-kyoto</t>
+  </si>
+  <si>
+    <t>קיוטו (תחנת קיוטו / שיג'ו)</t>
+  </si>
+  <si>
+    <t>Ayam-Ya Kyoto</t>
+  </si>
+  <si>
+    <t>¥1,000–1,600</t>
+  </si>
+  <si>
+    <t>100% חלאל, ללא חזיר</t>
+  </si>
+  <si>
+    <t>Tori Paitan Ramen / Spicy Ramen</t>
+  </si>
+  <si>
+    <t>Ayam Ya Kyoto Ramen</t>
+  </si>
+  <si>
+    <t>סניף של רשת הראמן חלאל על בסיס ציר עוף עשיר</t>
+  </si>
+  <si>
+    <t>chao-chao-gyoza</t>
+  </si>
+  <si>
+    <t>קיוטו (סאנג'ו / קוואראמאצ'י)</t>
+  </si>
+  <si>
+    <t>Chao Chao Gyoza Kyoto</t>
+  </si>
+  <si>
+    <t>גיוזה (כיסונים)</t>
+  </si>
+  <si>
+    <t>¥1,000–2,200</t>
+  </si>
+  <si>
+    <t>⚠️ מכיל חזיר! לחפש אופציות עוף/שרימפס/צמחוני</t>
+  </si>
+  <si>
+    <t>גיוזה עוף או גיוזה שרימפס</t>
+  </si>
+  <si>
+    <t>Chao Chao Gyoza Shijo Kawaramachi Kyoto</t>
+  </si>
+  <si>
+    <t>⚠️ מוסד הגיוזה המפורסם מגיש בעיקר גיוזות חזיר קלאסיות (חובה לבקש אופציות עוף/צמחוניות)</t>
+  </si>
+  <si>
+    <t>arashiyama-chikurin-tei</t>
+  </si>
+  <si>
+    <t>ארשייאמה (קיוטו)</t>
+  </si>
+  <si>
+    <t>Arashiyama Chikurin-tei</t>
+  </si>
+  <si>
+    <t>ראמן כשר / עוף</t>
+  </si>
+  <si>
+    <t>כשר / 100% ללא חזיר (ציר עוף)</t>
+  </si>
+  <si>
+    <t>ראמן עוף זך</t>
+  </si>
+  <si>
+    <t>Arashiyama Chikurin tei Kyoto</t>
+  </si>
+  <si>
+    <t>ראמן כשר ונקי לחלוטין מחזיר, המבוסס על ציר עוף באזור ארשייאמה</t>
+  </si>
+  <si>
+    <t>misono-osaka</t>
+  </si>
+  <si>
+    <t>אוסקה (אוเมדה / דוטונבורי)</t>
+  </si>
+  <si>
+    <t>Misono Osaka</t>
+  </si>
+  <si>
+    <t>ארוחת סטייק טפניאקי</t>
+  </si>
+  <si>
+    <t>Misono Teppanyaki Osaka</t>
+  </si>
+  <si>
+    <t>סניף נוסף של רשת הטפניאקי והסטייקים המציעה שואו מול העיניים</t>
   </si>
 </sst>
 </file>
@@ -2894,7 +4016,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2909,8 +4031,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2928,8 +4056,20 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F7FA"/>
+        <bgColor rgb="FFF2F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2961,11 +4101,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2991,11 +4159,82 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3083,8 +4322,11 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Restaurants" displayName="Restaurants" ref="A1:K7">
-  <autoFilter ref="A1:K7" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Restaurants" displayName="Restaurants" ref="A1:K45">
+  <autoFilter ref="A1:K45" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K45">
+    <sortCondition ref="B1:B45"/>
+  </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="מזהה"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="ימים"/>
@@ -3119,13 +4361,13 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Phrases" displayName="Phrases" ref="A1:D6">
-  <autoFilter ref="A1:D6" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Phrases" displayName="Phrases" ref="A1:D25" dataDxfId="4">
+  <autoFilter ref="A1:D25" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="קטגוריה"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="עברית"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="יפנית"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="תעתיק"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="קטגוריה" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="עברית" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="יפנית" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="תעתיק" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9622,7 +10864,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -9674,205 +10916,1463 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>849</v>
+      <c r="A2" s="16" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>1073</v>
+      </c>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20" t="s">
+        <v>1074</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="16" t="s">
+        <v>982</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>983</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>984</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>985</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>986</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>987</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>988</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>989</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>990</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>1055</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="19" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>1082</v>
+      </c>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="16" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>1124</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>1125</v>
+      </c>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>1156</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>1158</v>
+      </c>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>1206</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>1222</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>1223</v>
+      </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="17" t="s">
         <v>850</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B12" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C12" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D12" s="17" t="s">
         <v>851</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E12" s="17" t="s">
         <v>852</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F12" s="17" t="s">
         <v>853</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G12" s="17" t="s">
         <v>854</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H12" s="17" t="s">
         <v>852</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I12" s="17" t="s">
         <v>855</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
+      <c r="J12" s="17"/>
+      <c r="K12" s="17" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="17" t="s">
         <v>857</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B13" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C13" s="17" t="s">
         <v>858</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D13" s="17" t="s">
         <v>859</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E13" s="17" t="s">
         <v>860</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F13" s="17" t="s">
         <v>861</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G13" s="17" t="s">
         <v>862</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H13" s="17" t="s">
         <v>863</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I13" s="17" t="s">
         <v>864</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
+      <c r="J13" s="17"/>
+      <c r="K13" s="17" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+    <row r="14" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>877</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>1098</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>1188</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>1189</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>1190</v>
+      </c>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>1230</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>1231</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>1232</v>
+      </c>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A18" s="12" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>1263</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>1264</v>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>1269</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>1271</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>1272</v>
+      </c>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A20" s="14" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>1278</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>1281</v>
+      </c>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>1287</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>1288</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>1289</v>
+      </c>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A22" s="12" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>1294</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>1295</v>
+      </c>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="12" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>1246</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>1247</v>
+      </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="17" t="s">
         <v>866</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B24" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C24" s="17" t="s">
         <v>725</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D24" s="17" t="s">
         <v>867</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E24" s="17" t="s">
         <v>868</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F24" s="17" t="s">
         <v>869</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G24" s="17" t="s">
         <v>870</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H24" s="17" t="s">
         <v>871</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I24" s="17" t="s">
         <v>872</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2" t="s">
+      <c r="J24" s="17"/>
+      <c r="K24" s="17" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+    <row r="25" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="12" t="s">
+        <v>992</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>993</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>995</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>996</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>997</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>998</v>
+      </c>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A26" s="12" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="10" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>1039</v>
+      </c>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A28" s="10" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>1105</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>1107</v>
+      </c>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A29" s="12" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>1116</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>1117</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="12" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>1180</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>1181</v>
+      </c>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="14" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>1196</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>1197</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="17" t="s">
         <v>873</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B32" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C32" s="17" t="s">
         <v>874</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D32" s="17" t="s">
         <v>875</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E32" s="17" t="s">
         <v>876</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F32" s="17" t="s">
         <v>877</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G32" s="17" t="s">
         <v>878</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H32" s="17" t="s">
         <v>879</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I32" s="17" t="s">
         <v>880</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2" t="s">
+      <c r="J32" s="17"/>
+      <c r="K32" s="17" t="s">
         <v>881</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+    <row r="33" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="17" t="s">
         <v>882</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B33" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C33" s="17" t="s">
         <v>757</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D33" s="17" t="s">
         <v>883</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E33" s="17" t="s">
         <v>884</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F33" s="17" t="s">
         <v>885</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G33" s="17" t="s">
         <v>886</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H33" s="17" t="s">
         <v>887</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I33" s="17" t="s">
         <v>888</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J33" s="17" t="s">
         <v>889</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K33" s="17" t="s">
         <v>890</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="10" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>1007</v>
+      </c>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="12" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>757</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>1014</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>1015</v>
+      </c>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="10" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>757</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>1021</v>
+      </c>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A37" s="12" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>757</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>1047</v>
+      </c>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A38" s="14" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>874</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>1064</v>
+      </c>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A39" s="10" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>1090</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>1091</v>
+      </c>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="12" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>874</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>1131</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>1132</v>
+      </c>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A41" s="10" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>1139</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>1140</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>1141</v>
+      </c>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="12" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>757</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>1165</v>
+      </c>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="10" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>757</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>1172</v>
+      </c>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="14" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H44" s="15" t="s">
+        <v>1236</v>
+      </c>
+      <c r="I44" s="15" t="s">
+        <v>1239</v>
+      </c>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="18" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>1253</v>
+      </c>
+      <c r="G45" s="21" t="s">
+        <v>1254</v>
+      </c>
+      <c r="H45" s="21" t="s">
+        <v>1255</v>
+      </c>
+      <c r="I45" s="21" t="s">
+        <v>1256</v>
+      </c>
+      <c r="J45" s="21"/>
+      <c r="K45" s="21" t="s">
+        <v>1257</v>
       </c>
     </row>
   </sheetData>
@@ -10063,7 +12563,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -10071,7 +12571,7 @@
     <col min="4" max="4" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>902</v>
       </c>
@@ -10085,74 +12585,340 @@
         <v>905</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>907</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>908</v>
       </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>909</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>906</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>910</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>911</v>
       </c>
-      <c r="D3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>912</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>906</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="D4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B5" t="s">
+        <v>923</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B6" t="s">
+        <v>926</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B7" t="s">
+        <v>929</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B8" t="s">
+        <v>932</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B9" t="s">
+        <v>935</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B10" t="s">
+        <v>938</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B11" t="s">
+        <v>941</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="B13" t="s">
+        <v>945</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="B14" t="s">
+        <v>948</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="B15" t="s">
+        <v>951</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="B16" t="s">
+        <v>954</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="B17" t="s">
+        <v>957</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="B18" t="s">
+        <v>960</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>915</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="C19" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>920</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>921</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>922</v>
+      <c r="B20" t="s">
+        <v>963</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B21" t="s">
+        <v>966</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>969</v>
+      </c>
+      <c r="B22" t="s">
+        <v>970</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>969</v>
+      </c>
+      <c r="B23" t="s">
+        <v>973</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>969</v>
+      </c>
+      <c r="B24" t="s">
+        <v>976</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>969</v>
+      </c>
+      <c r="B25" t="s">
+        <v>979</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>981</v>
       </c>
     </row>
   </sheetData>
